--- a/Team-Data/2013-14/3-31-2013-14.xlsx
+++ b/Team-Data/2013-14/3-31-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="n">
         <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>0.438</v>
+        <v>0.431</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L2" t="n">
         <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.366</v>
+        <v>0.369</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P2" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.78</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="U2" t="n">
         <v>24.8</v>
@@ -730,25 +797,25 @@
         <v>19.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
@@ -760,10 +827,10 @@
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
@@ -772,16 +839,16 @@
         <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ2" t="n">
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -796,10 +863,10 @@
         <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>0.311</v>
+        <v>0.315</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J3" t="n">
-        <v>83.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>0.433</v>
@@ -870,34 +937,34 @@
         <v>6.7</v>
       </c>
       <c r="M3" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="O3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="P3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R3" t="n">
         <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T3" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V3" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
         <v>7.1</v>
@@ -906,22 +973,22 @@
         <v>4.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4.2</v>
+        <v>-4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -942,7 +1009,7 @@
         <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>23</v>
@@ -966,10 +1033,10 @@
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
         <v>25</v>
@@ -978,13 +1045,13 @@
         <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -993,7 +1060,7 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
         <v>25</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1118,7 +1185,7 @@
         <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
@@ -1142,10 +1209,10 @@
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1163,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.486</v>
+        <v>0.479</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1231,25 +1298,25 @@
         <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.74</v>
+        <v>0.738</v>
       </c>
       <c r="R5" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S5" t="n">
         <v>32.8</v>
@@ -1261,7 +1328,7 @@
         <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W5" t="n">
         <v>6.1</v>
@@ -1270,25 +1337,25 @@
         <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA5" t="n">
         <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1306,7 +1373,7 @@
         <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
         <v>26</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1413,34 +1480,34 @@
         <v>0.43</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R6" t="n">
         <v>11.6</v>
       </c>
       <c r="S6" t="n">
-        <v>32.9</v>
+        <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U6" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V6" t="n">
         <v>15.2</v>
@@ -1458,25 +1525,25 @@
         <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>4</v>
@@ -1488,10 +1555,10 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>28</v>
@@ -1503,13 +1570,13 @@
         <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
@@ -1527,7 +1594,7 @@
         <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1737,7 @@
         <v>9</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>18</v>
@@ -1682,7 +1749,7 @@
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP7" t="n">
         <v>18</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1867,7 +1934,7 @@
         <v>16</v>
       </c>
       <c r="AP8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1882,7 +1949,7 @@
         <v>26</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
         <v>4</v>
@@ -1891,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" t="n">
         <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,10 +2020,10 @@
         <v>38.1</v>
       </c>
       <c r="J9" t="n">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L9" t="n">
         <v>8.4</v>
@@ -1968,13 +2035,13 @@
         <v>0.359</v>
       </c>
       <c r="O9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P9" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="R9" t="n">
         <v>12.2</v>
@@ -1995,34 +2062,34 @@
         <v>7.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y9" t="n">
         <v>5.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.6</v>
+        <v>103.7</v>
       </c>
       <c r="AC9" t="n">
         <v>-2.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>28</v>
@@ -2037,7 +2104,7 @@
         <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2061,7 +2128,7 @@
         <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
         <v>12</v>
@@ -2076,7 +2143,7 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ9" t="n">
         <v>28</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="n">
         <v>47</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365</v>
+        <v>0.356</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>86.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.448</v>
       </c>
       <c r="L10" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M10" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="N10" t="n">
-        <v>0.318</v>
+        <v>0.317</v>
       </c>
       <c r="O10" t="n">
         <v>16.8</v>
       </c>
       <c r="P10" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.669</v>
+        <v>0.668</v>
       </c>
       <c r="R10" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="S10" t="n">
         <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="U10" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V10" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W10" t="n">
         <v>8.5</v>
@@ -2180,22 +2247,22 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA10" t="n">
         <v>20.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.7</v>
+        <v>100.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>6</v>
@@ -2216,10 +2283,10 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
@@ -2240,16 +2307,16 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU10" t="n">
         <v>21</v>
       </c>
-      <c r="AT10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>19</v>
-      </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2261,13 +2328,13 @@
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
         <v>15</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>17</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>15</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2413,7 +2480,7 @@
         <v>21</v>
       </c>
       <c r="AP11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ11" t="n">
         <v>18</v>
@@ -2428,7 +2495,7 @@
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
         <v>22</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>5.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
@@ -2607,7 +2674,7 @@
         <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
         <v>20</v>
@@ -2616,7 +2683,7 @@
         <v>29</v>
       </c>
       <c r="AW12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2730,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
         <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.703</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J13" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
         <v>18.3</v>
@@ -2705,19 +2772,19 @@
         <v>0.784</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="T13" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U13" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W13" t="n">
         <v>6.9</v>
@@ -2735,34 +2802,34 @@
         <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ13" t="n">
         <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
         <v>24</v>
@@ -2771,7 +2838,7 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2789,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AU13" t="n">
         <v>28</v>
@@ -2804,20 +2871,20 @@
         <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
         <v>13</v>
       </c>
       <c r="BA13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC13" t="n">
         <v>5</v>
       </c>
-      <c r="BB13" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>6</v>
-      </c>
       <c r="BD13" t="n">
         <v>10</v>
       </c>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.707</v>
+        <v>0.703</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2872,19 +2939,19 @@
         <v>8.4</v>
       </c>
       <c r="M14" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R14" t="n">
         <v>10.5</v>
@@ -2893,19 +2960,19 @@
         <v>32.4</v>
       </c>
       <c r="T14" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U14" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="V14" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>3.4</v>
@@ -2917,13 +2984,13 @@
         <v>23.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.6</v>
+        <v>107.5</v>
       </c>
       <c r="AC14" t="n">
         <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
@@ -2947,13 +3014,13 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2971,7 +3038,7 @@
         <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF15" t="n">
         <v>24</v>
       </c>
       <c r="AG15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
         <v>30</v>
@@ -3123,7 +3190,7 @@
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
         <v>14</v>
@@ -3153,7 +3220,7 @@
         <v>15</v>
       </c>
       <c r="AT15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU15" t="n">
         <v>4</v>
@@ -3174,7 +3241,7 @@
         <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
         <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>0.595</v>
+        <v>0.589</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3236,22 +3303,22 @@
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O16" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="R16" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="S16" t="n">
         <v>30.9</v>
@@ -3278,7 +3345,7 @@
         <v>19.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB16" t="n">
         <v>95.59999999999999</v>
@@ -3287,19 +3354,19 @@
         <v>1.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3329,10 +3396,10 @@
         <v>23</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT16" t="n">
         <v>20</v>
@@ -3347,7 +3414,7 @@
         <v>13</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3359,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F17" t="n">
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.699</v>
+        <v>0.694</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
-        <v>76.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="K17" t="n">
         <v>0.504</v>
@@ -3421,7 +3488,7 @@
         <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O17" t="n">
         <v>17.7</v>
@@ -3430,7 +3497,7 @@
         <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R17" t="n">
         <v>7.6</v>
@@ -3451,7 +3518,7 @@
         <v>8.9</v>
       </c>
       <c r="X17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y17" t="n">
         <v>3</v>
@@ -3460,16 +3527,16 @@
         <v>19.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>102.9</v>
+        <v>103</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3478,13 +3545,13 @@
         <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
         <v>11</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,16 +3566,16 @@
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
       </c>
       <c r="AP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>15</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3520,16 +3587,16 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>2</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
         <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
@@ -3591,46 +3658,46 @@
         <v>35.9</v>
       </c>
       <c r="J18" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.434</v>
       </c>
       <c r="L18" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>19.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O18" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="P18" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R18" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S18" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T18" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X18" t="n">
         <v>4.9</v>
@@ -3642,16 +3709,16 @@
         <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.3</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,10 +3733,10 @@
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
@@ -3684,10 +3751,10 @@
         <v>18</v>
       </c>
       <c r="AO18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AQ18" t="n">
         <v>20</v>
@@ -3699,7 +3766,7 @@
         <v>30</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E19" t="n">
         <v>36</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>0.493</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>38.8</v>
       </c>
       <c r="J19" t="n">
-        <v>87.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.443</v>
@@ -3782,22 +3849,22 @@
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="N19" t="n">
         <v>0.344</v>
       </c>
       <c r="O19" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="P19" t="n">
-        <v>27.7</v>
+        <v>27.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0.78</v>
       </c>
       <c r="R19" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S19" t="n">
         <v>32.3</v>
@@ -3806,10 +3873,10 @@
         <v>44.9</v>
       </c>
       <c r="U19" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V19" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W19" t="n">
         <v>8.699999999999999</v>
@@ -3821,19 +3888,19 @@
         <v>5.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.7</v>
+        <v>106.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3848,7 +3915,7 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
@@ -3884,7 +3951,7 @@
         <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
         <v>5</v>
@@ -3896,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>0.432</v>
+        <v>0.438</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L20" t="n">
         <v>5.9</v>
@@ -3973,19 +4040,19 @@
         <v>18.1</v>
       </c>
       <c r="P20" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q20" t="n">
         <v>0.771</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U20" t="n">
         <v>21.2</v>
@@ -3994,37 +4061,37 @@
         <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X20" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
         <v>22.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC20" t="n">
         <v>-2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>18</v>
       </c>
       <c r="AF20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH20" t="n">
         <v>8</v>
@@ -4033,7 +4100,7 @@
         <v>14</v>
       </c>
       <c r="AJ20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
@@ -4057,7 +4124,7 @@
         <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -4119,61 +4186,61 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" t="n">
         <v>43</v>
       </c>
       <c r="G21" t="n">
-        <v>0.427</v>
+        <v>0.419</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J21" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L21" t="n">
         <v>9.1</v>
       </c>
       <c r="M21" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O21" t="n">
         <v>15.2</v>
       </c>
       <c r="P21" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U21" t="n">
         <v>20.3</v>
       </c>
       <c r="V21" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W21" t="n">
         <v>7.5</v>
@@ -4185,22 +4252,22 @@
         <v>3.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
         <v>21</v>
@@ -4215,10 +4282,10 @@
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4239,13 +4306,13 @@
         <v>17</v>
       </c>
       <c r="AR21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
       </c>
       <c r="AT21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU21" t="n">
         <v>26</v>
@@ -4260,7 +4327,7 @@
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4397,7 +4464,7 @@
         <v>4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4409,13 +4476,13 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4427,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4436,13 +4503,13 @@
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
       </c>
       <c r="AY22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4573,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
         <v>21</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO23" t="n">
         <v>26</v>
@@ -4624,7 +4691,7 @@
         <v>24</v>
       </c>
       <c r="AY23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
         <v>10</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -4665,73 +4732,73 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24" t="n">
         <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G24" t="n">
-        <v>0.216</v>
+        <v>0.219</v>
       </c>
       <c r="H24" t="n">
         <v>48.5</v>
       </c>
       <c r="I24" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J24" t="n">
-        <v>87.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.43</v>
       </c>
       <c r="L24" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M24" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.311</v>
+        <v>0.31</v>
       </c>
       <c r="O24" t="n">
         <v>16.4</v>
       </c>
       <c r="P24" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.709</v>
+        <v>0.71</v>
       </c>
       <c r="R24" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S24" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T24" t="n">
         <v>43.4</v>
       </c>
       <c r="U24" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V24" t="n">
         <v>17.2</v>
       </c>
       <c r="W24" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Z24" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA24" t="n">
         <v>20.7</v>
@@ -4743,7 +4810,7 @@
         <v>-11</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4764,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL24" t="n">
         <v>19</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>17</v>
@@ -4785,7 +4852,7 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS24" t="n">
         <v>17</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
@@ -4937,10 +5004,10 @@
         <v>9</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ25" t="n">
         <v>11</v>
@@ -4949,7 +5016,7 @@
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
@@ -4967,7 +5034,7 @@
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4979,19 +5046,19 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
         <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" t="n">
         <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.351</v>
+        <v>0.342</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
@@ -5238,16 +5305,16 @@
         <v>6.2</v>
       </c>
       <c r="M27" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N27" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O27" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P27" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.763</v>
@@ -5280,16 +5347,16 @@
         <v>22.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AB27" t="n">
         <v>101</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5310,7 +5377,7 @@
         <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5343,19 +5410,19 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW27" t="n">
         <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA27" t="n">
         <v>4</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E28" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.784</v>
+        <v>0.781</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
@@ -5411,7 +5478,7 @@
         <v>40.6</v>
       </c>
       <c r="J28" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.489</v>
@@ -5423,34 +5490,34 @@
         <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="O28" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S28" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="T28" t="n">
         <v>43.3</v>
       </c>
       <c r="U28" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="V28" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X28" t="n">
         <v>5.3</v>
@@ -5468,10 +5535,10 @@
         <v>105.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5507,10 +5574,10 @@
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR28" t="n">
         <v>27</v>
@@ -5525,10 +5592,10 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -5575,55 +5642,55 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" t="n">
         <v>42</v>
       </c>
       <c r="F29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="H29" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I29" t="n">
         <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K29" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
         <v>8.4</v>
       </c>
       <c r="M29" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.366</v>
+        <v>0.367</v>
       </c>
       <c r="O29" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="P29" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.783</v>
+        <v>0.784</v>
       </c>
       <c r="R29" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S29" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T29" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="U29" t="n">
         <v>21.2</v>
@@ -5635,7 +5702,7 @@
         <v>7.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
         <v>4.4</v>
@@ -5644,16 +5711,16 @@
         <v>22.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5689,10 +5756,10 @@
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
         <v>12</v>
@@ -5701,10 +5768,10 @@
         <v>19</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV29" t="n">
         <v>9</v>
@@ -5713,19 +5780,19 @@
         <v>23</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
       </c>
       <c r="AZ29" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
         <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G30" t="n">
-        <v>0.307</v>
+        <v>0.311</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5778,46 +5845,46 @@
         <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L30" t="n">
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N30" t="n">
         <v>0.35</v>
       </c>
       <c r="O30" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P30" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
       </c>
       <c r="V30" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W30" t="n">
         <v>6.8</v>
       </c>
       <c r="X30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
@@ -5826,16 +5893,16 @@
         <v>20.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="AC30" t="n">
         <v>-7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5850,13 +5917,13 @@
         <v>29</v>
       </c>
       <c r="AI30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ30" t="n">
         <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
         <v>22</v>
@@ -5871,13 +5938,13 @@
         <v>24</v>
       </c>
       <c r="AP30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AQ30" t="n">
         <v>22</v>
       </c>
       <c r="AR30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -5889,7 +5956,7 @@
         <v>27</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
@@ -5904,7 +5971,7 @@
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E31" t="n">
         <v>38</v>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.514</v>
+        <v>0.521</v>
       </c>
       <c r="H31" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I31" t="n">
         <v>38.5</v>
       </c>
       <c r="J31" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K31" t="n">
         <v>0.455</v>
@@ -5966,19 +6033,19 @@
         <v>8.1</v>
       </c>
       <c r="M31" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N31" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="O31" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R31" t="n">
         <v>11</v>
@@ -6002,22 +6069,22 @@
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
         <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC31" t="n">
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6035,10 +6102,10 @@
         <v>11</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6062,7 +6129,7 @@
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT31" t="n">
         <v>19</v>
@@ -6074,7 +6141,7 @@
         <v>15</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>15</v>
@@ -6089,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-31-2013-14</t>
+          <t>2014-03-31</t>
         </is>
       </c>
     </row>
